--- a/ministry/2027_사역신청_부서확인양식.xlsx
+++ b/ministry/2027_사역신청_부서확인양식.xlsx
@@ -628,7 +628,7 @@
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>문의: 제자양육부 신앙운동팀</t>
+          <t>문의: 방송전산부 전산팀</t>
         </is>
       </c>
     </row>

--- a/ministry/2027_사역신청_부서확인양식.xlsx
+++ b/ministry/2027_사역신청_부서확인양식.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="임명직 전용 부서" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$2:$T$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$2:$X$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -182,8 +182,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
@@ -194,8 +197,11 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
@@ -206,8 +212,11 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -636,7 +645,7 @@
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>② 언제 — 여섯 칸 (2026-09-10 추가)</t>
+          <t>② 언제 — 열 칸 (2026-09-10)</t>
         </is>
       </c>
     </row>
@@ -650,21 +659,21 @@
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · J·K·L열 (주일 / 평일 / 토요일) — 해당하는 칸에 O 를 넣어 주세요. 여럿이면 여럿 다 넣습니다.</t>
+          <t xml:space="preserve">  · J~M열 (주일 / 금요일 / 토요일 / 평일) — 해당하는 칸마다 O. 여럿이면 여럿 다 넣습니다. ⚠️ 금요일은 따로 두었으니 M열 '평일'은 **금요일을 뺀 날**(월~목)로 봐 주세요 — 금요성령집회·행복전도대(금)처럼 금요일 사역이 많아 성도가 금요일만 골라 찾을 수 있게 나눴습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · M·N열 (시작 시각 / 끝 시각) — 24시간 꼴로 적어 주세요. 보기: 05:00, 09:30, 14:00, 20:00.</t>
+          <t xml:space="preserve">  · N~Q열 (매주 / 격주(교대형식) / 매달 / 그때그때) — 해당하는 칸마다 O. **여럿 고를 수 있습니다** (매주 또는 격주인 팀이 있습니다). ⚠️ **팀이 모이는 주기가 아니라, 한 분이 실제로 서는 주기**입니다. 당번을 넷이 돌아가며 서면 팀은 매주라도 한 분은 '매달'입니다 — 성도님이 재는 것은 자기 부담입니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · O열 (한 사람이 서는 주기) — **팀이 모이는 주기가 아니라, 한 분이 실제로 서는 주기**입니다. 당번을 넷이 돌아가며 서면 팀은 매주라도 한 분은 '매달'입니다. 성도님이 재는 것은 자기 부담입니다.</t>
+          <t xml:space="preserve">  · R·S열 (주일 시작 시각 / 주일 끝 시각) — 24시간 꼴로. 보기: 09:30, 14:00. ⚠️ **주일 사역에만** 적습니다. 평일·금요일·토요일 사역의 시간은 아래 ③의 문장 칸에 적어 주세요.</t>
         </is>
       </c>
     </row>
@@ -685,21 +694,21 @@
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · P열 '사역 시간·요일(문장으로)' — 사람이 읽는 한 줄입니다. 보기: '매주 화 오전 10시, 예배 30분 전 모임'.</t>
+          <t xml:space="preserve">  · T열 '사역 시간·요일(문장으로)' — 사람이 읽는 한 줄입니다. 보기: '매주 화 오전 10시, 예배 30분 전 모임'. 주일이 아닌 사역의 시간은 여기에 적어 주세요.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · Q열 '하는 일 — 한 줄' — 이름만 보고는 알 수 없는 것을 적어 주세요(예: 오병이어 1팀·2팀이 무엇이 다른지). 짧게만 적으셔도 됩니다.</t>
+          <t xml:space="preserve">  · U열 '하는 일 — 한 줄' — 이름만 보고는 알 수 없는 것을 적어 주세요(예: 오병이어 1팀·2팀이 무엇이 다른지). 짧게만 적으셔도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · R열 '필요 인원'은 선택입니다 — 정원을 세거나 신청을 막는 데 쓰지 않고 참고로만 보여드립니다.</t>
+          <t xml:space="preserve">  · V열 '필요 인원'은 선택입니다 — 정원을 세거나 신청을 막는 데 쓰지 않고 참고로만 보여드립니다.</t>
         </is>
       </c>
     </row>
@@ -713,7 +722,7 @@
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>S열에 확인하신 분 성함을, T열에는 그 밖에 전달할 내용을 적어 주세요.</t>
+          <t>W열에 확인하신 분 성함을, X열에는 그 밖에 전달할 내용을 적어 주세요.</t>
         </is>
       </c>
     </row>
@@ -763,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T96"/>
+  <dimension ref="A1:X96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -776,16 +785,20 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -801,15 +814,15 @@
       </c>
       <c r="J1" s="7" t="inlineStr">
         <is>
-          <t>② 언제 — 성도님이 이 여섯 칸으로 사역을 찾습니다</t>
-        </is>
-      </c>
-      <c r="P1" s="7" t="inlineStr">
+          <t>② 언제 — 성도님이 이 칸들로 사역을 찾습니다</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>③ 성도님 화면에 그대로 보일 안내</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>④ 확인</t>
         </is>
@@ -868,7 +881,7 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>평일</t>
+          <t>금요일</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -878,40 +891,60 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>시작 시각</t>
+          <t>평일(금 제외)</t>
         </is>
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>끝 시각</t>
+          <t>매주</t>
         </is>
       </c>
       <c r="O2" s="8" t="inlineStr">
         <is>
-          <t>한 사람이 서는 주기</t>
+          <t>격주(교대형식)</t>
         </is>
       </c>
       <c r="P2" s="8" t="inlineStr">
         <is>
+          <t>매달</t>
+        </is>
+      </c>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>그때그때</t>
+        </is>
+      </c>
+      <c r="R2" s="8" t="inlineStr">
+        <is>
+          <t>주일 시작 시각</t>
+        </is>
+      </c>
+      <c r="S2" s="8" t="inlineStr">
+        <is>
+          <t>주일 끝 시각</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
           <t>사역 시간·요일 (문장으로)</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>하는 일 — 한 줄</t>
         </is>
       </c>
-      <c r="R2" s="8" t="inlineStr">
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>필요 인원 (선택)</t>
         </is>
       </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="W2" s="8" t="inlineStr">
         <is>
           <t>확인하신 분 (성명)</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
+      <c r="X2" s="8" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -945,13 +978,17 @@
       <c r="K3" s="14" t="n"/>
       <c r="L3" s="14" t="n"/>
       <c r="M3" s="15" t="n"/>
-      <c r="N3" s="15" t="n"/>
-      <c r="O3" s="12" t="n"/>
-      <c r="P3" s="12" t="n"/>
-      <c r="Q3" s="12" t="n"/>
-      <c r="R3" s="12" t="n"/>
-      <c r="S3" s="12" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="15" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="16" t="n"/>
       <c r="T3" s="12" t="n"/>
+      <c r="U3" s="12" t="n"/>
+      <c r="V3" s="12" t="n"/>
+      <c r="W3" s="12" t="n"/>
+      <c r="X3" s="12" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n">
@@ -981,13 +1018,17 @@
       <c r="K4" s="14" t="n"/>
       <c r="L4" s="14" t="n"/>
       <c r="M4" s="15" t="n"/>
-      <c r="N4" s="15" t="n"/>
-      <c r="O4" s="12" t="n"/>
-      <c r="P4" s="12" t="n"/>
-      <c r="Q4" s="12" t="n"/>
-      <c r="R4" s="12" t="n"/>
-      <c r="S4" s="12" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="15" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="16" t="n"/>
+      <c r="S4" s="16" t="n"/>
       <c r="T4" s="12" t="n"/>
+      <c r="U4" s="12" t="n"/>
+      <c r="V4" s="12" t="n"/>
+      <c r="W4" s="12" t="n"/>
+      <c r="X4" s="12" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -1017,13 +1058,17 @@
       <c r="K5" s="14" t="n"/>
       <c r="L5" s="14" t="n"/>
       <c r="M5" s="15" t="n"/>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="12" t="n"/>
-      <c r="R5" s="12" t="n"/>
-      <c r="S5" s="12" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="15" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="16" t="n"/>
+      <c r="S5" s="16" t="n"/>
       <c r="T5" s="12" t="n"/>
+      <c r="U5" s="12" t="n"/>
+      <c r="V5" s="12" t="n"/>
+      <c r="W5" s="12" t="n"/>
+      <c r="X5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1061,13 +1106,17 @@
       <c r="K6" s="14" t="n"/>
       <c r="L6" s="14" t="n"/>
       <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="12" t="n"/>
-      <c r="R6" s="12" t="n"/>
-      <c r="S6" s="12" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="15" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="16" t="n"/>
       <c r="T6" s="12" t="n"/>
+      <c r="U6" s="12" t="n"/>
+      <c r="V6" s="12" t="n"/>
+      <c r="W6" s="12" t="n"/>
+      <c r="X6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -1105,13 +1154,17 @@
       <c r="K7" s="14" t="n"/>
       <c r="L7" s="14" t="n"/>
       <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="12" t="n"/>
-      <c r="R7" s="12" t="n"/>
-      <c r="S7" s="12" t="n"/>
+      <c r="N7" s="14" t="n"/>
+      <c r="O7" s="15" t="n"/>
+      <c r="P7" s="14" t="n"/>
+      <c r="Q7" s="14" t="n"/>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="n"/>
       <c r="T7" s="12" t="n"/>
+      <c r="U7" s="12" t="n"/>
+      <c r="V7" s="12" t="n"/>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -1149,13 +1202,17 @@
       <c r="K8" s="14" t="n"/>
       <c r="L8" s="14" t="n"/>
       <c r="M8" s="15" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="12" t="n"/>
-      <c r="R8" s="12" t="n"/>
-      <c r="S8" s="12" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="15" t="n"/>
+      <c r="P8" s="14" t="n"/>
+      <c r="Q8" s="14" t="n"/>
+      <c r="R8" s="16" t="n"/>
+      <c r="S8" s="16" t="n"/>
       <c r="T8" s="12" t="n"/>
+      <c r="U8" s="12" t="n"/>
+      <c r="V8" s="12" t="n"/>
+      <c r="W8" s="12" t="n"/>
+      <c r="X8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -1193,13 +1250,17 @@
       <c r="K9" s="14" t="n"/>
       <c r="L9" s="14" t="n"/>
       <c r="M9" s="15" t="n"/>
-      <c r="N9" s="15" t="n"/>
-      <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="12" t="n"/>
-      <c r="R9" s="12" t="n"/>
-      <c r="S9" s="12" t="n"/>
+      <c r="N9" s="14" t="n"/>
+      <c r="O9" s="15" t="n"/>
+      <c r="P9" s="14" t="n"/>
+      <c r="Q9" s="14" t="n"/>
+      <c r="R9" s="16" t="n"/>
+      <c r="S9" s="16" t="n"/>
       <c r="T9" s="12" t="n"/>
+      <c r="U9" s="12" t="n"/>
+      <c r="V9" s="12" t="n"/>
+      <c r="W9" s="12" t="n"/>
+      <c r="X9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -1233,13 +1294,17 @@
       <c r="K10" s="14" t="n"/>
       <c r="L10" s="14" t="n"/>
       <c r="M10" s="15" t="n"/>
-      <c r="N10" s="15" t="n"/>
-      <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="12" t="n"/>
-      <c r="R10" s="12" t="n"/>
-      <c r="S10" s="12" t="n"/>
+      <c r="N10" s="14" t="n"/>
+      <c r="O10" s="15" t="n"/>
+      <c r="P10" s="14" t="n"/>
+      <c r="Q10" s="14" t="n"/>
+      <c r="R10" s="16" t="n"/>
+      <c r="S10" s="16" t="n"/>
       <c r="T10" s="12" t="n"/>
+      <c r="U10" s="12" t="n"/>
+      <c r="V10" s="12" t="n"/>
+      <c r="W10" s="12" t="n"/>
+      <c r="X10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1273,13 +1338,17 @@
       <c r="K11" s="14" t="n"/>
       <c r="L11" s="14" t="n"/>
       <c r="M11" s="15" t="n"/>
-      <c r="N11" s="15" t="n"/>
-      <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="12" t="n"/>
-      <c r="R11" s="12" t="n"/>
-      <c r="S11" s="12" t="n"/>
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="15" t="n"/>
+      <c r="P11" s="14" t="n"/>
+      <c r="Q11" s="14" t="n"/>
+      <c r="R11" s="16" t="n"/>
+      <c r="S11" s="16" t="n"/>
       <c r="T11" s="12" t="n"/>
+      <c r="U11" s="12" t="n"/>
+      <c r="V11" s="12" t="n"/>
+      <c r="W11" s="12" t="n"/>
+      <c r="X11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -1313,13 +1382,17 @@
       <c r="K12" s="14" t="n"/>
       <c r="L12" s="14" t="n"/>
       <c r="M12" s="15" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
-      <c r="Q12" s="12" t="n"/>
-      <c r="R12" s="12" t="n"/>
-      <c r="S12" s="12" t="n"/>
+      <c r="N12" s="14" t="n"/>
+      <c r="O12" s="15" t="n"/>
+      <c r="P12" s="14" t="n"/>
+      <c r="Q12" s="14" t="n"/>
+      <c r="R12" s="16" t="n"/>
+      <c r="S12" s="16" t="n"/>
       <c r="T12" s="12" t="n"/>
+      <c r="U12" s="12" t="n"/>
+      <c r="V12" s="12" t="n"/>
+      <c r="W12" s="12" t="n"/>
+      <c r="X12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -1353,13 +1426,17 @@
       <c r="K13" s="14" t="n"/>
       <c r="L13" s="14" t="n"/>
       <c r="M13" s="15" t="n"/>
-      <c r="N13" s="15" t="n"/>
-      <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-      <c r="Q13" s="12" t="n"/>
-      <c r="R13" s="12" t="n"/>
-      <c r="S13" s="12" t="n"/>
+      <c r="N13" s="14" t="n"/>
+      <c r="O13" s="15" t="n"/>
+      <c r="P13" s="14" t="n"/>
+      <c r="Q13" s="14" t="n"/>
+      <c r="R13" s="16" t="n"/>
+      <c r="S13" s="16" t="n"/>
       <c r="T13" s="12" t="n"/>
+      <c r="U13" s="12" t="n"/>
+      <c r="V13" s="12" t="n"/>
+      <c r="W13" s="12" t="n"/>
+      <c r="X13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -1393,13 +1470,17 @@
       <c r="K14" s="14" t="n"/>
       <c r="L14" s="14" t="n"/>
       <c r="M14" s="15" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
-      <c r="Q14" s="12" t="n"/>
-      <c r="R14" s="12" t="n"/>
-      <c r="S14" s="12" t="n"/>
+      <c r="N14" s="14" t="n"/>
+      <c r="O14" s="15" t="n"/>
+      <c r="P14" s="14" t="n"/>
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="16" t="n"/>
+      <c r="S14" s="16" t="n"/>
       <c r="T14" s="12" t="n"/>
+      <c r="U14" s="12" t="n"/>
+      <c r="V14" s="12" t="n"/>
+      <c r="W14" s="12" t="n"/>
+      <c r="X14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -1433,13 +1514,17 @@
       <c r="K15" s="14" t="n"/>
       <c r="L15" s="14" t="n"/>
       <c r="M15" s="15" t="n"/>
-      <c r="N15" s="15" t="n"/>
-      <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
-      <c r="Q15" s="12" t="n"/>
-      <c r="R15" s="12" t="n"/>
-      <c r="S15" s="12" t="n"/>
+      <c r="N15" s="14" t="n"/>
+      <c r="O15" s="15" t="n"/>
+      <c r="P15" s="14" t="n"/>
+      <c r="Q15" s="14" t="n"/>
+      <c r="R15" s="16" t="n"/>
+      <c r="S15" s="16" t="n"/>
       <c r="T15" s="12" t="n"/>
+      <c r="U15" s="12" t="n"/>
+      <c r="V15" s="12" t="n"/>
+      <c r="W15" s="12" t="n"/>
+      <c r="X15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -1473,13 +1558,17 @@
       <c r="K16" s="14" t="n"/>
       <c r="L16" s="14" t="n"/>
       <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="12" t="n"/>
-      <c r="R16" s="12" t="n"/>
-      <c r="S16" s="12" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+      <c r="R16" s="16" t="n"/>
+      <c r="S16" s="16" t="n"/>
       <c r="T16" s="12" t="n"/>
+      <c r="U16" s="12" t="n"/>
+      <c r="V16" s="12" t="n"/>
+      <c r="W16" s="12" t="n"/>
+      <c r="X16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -1513,13 +1602,17 @@
       <c r="K17" s="14" t="n"/>
       <c r="L17" s="14" t="n"/>
       <c r="M17" s="15" t="n"/>
-      <c r="N17" s="15" t="n"/>
-      <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="12" t="n"/>
-      <c r="R17" s="12" t="n"/>
-      <c r="S17" s="12" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="14" t="n"/>
+      <c r="Q17" s="14" t="n"/>
+      <c r="R17" s="16" t="n"/>
+      <c r="S17" s="16" t="n"/>
       <c r="T17" s="12" t="n"/>
+      <c r="U17" s="12" t="n"/>
+      <c r="V17" s="12" t="n"/>
+      <c r="W17" s="12" t="n"/>
+      <c r="X17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -1553,13 +1646,17 @@
       <c r="K18" s="14" t="n"/>
       <c r="L18" s="14" t="n"/>
       <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="12" t="n"/>
-      <c r="R18" s="12" t="n"/>
-      <c r="S18" s="12" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="16" t="n"/>
+      <c r="S18" s="16" t="n"/>
       <c r="T18" s="12" t="n"/>
+      <c r="U18" s="12" t="n"/>
+      <c r="V18" s="12" t="n"/>
+      <c r="W18" s="12" t="n"/>
+      <c r="X18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -1593,13 +1690,17 @@
       <c r="K19" s="14" t="n"/>
       <c r="L19" s="14" t="n"/>
       <c r="M19" s="15" t="n"/>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="12" t="n"/>
-      <c r="P19" s="12" t="n"/>
-      <c r="Q19" s="12" t="n"/>
-      <c r="R19" s="12" t="n"/>
-      <c r="S19" s="12" t="n"/>
+      <c r="N19" s="14" t="n"/>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="14" t="n"/>
+      <c r="Q19" s="14" t="n"/>
+      <c r="R19" s="16" t="n"/>
+      <c r="S19" s="16" t="n"/>
       <c r="T19" s="12" t="n"/>
+      <c r="U19" s="12" t="n"/>
+      <c r="V19" s="12" t="n"/>
+      <c r="W19" s="12" t="n"/>
+      <c r="X19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -1633,49 +1734,57 @@
       <c r="K20" s="14" t="n"/>
       <c r="L20" s="14" t="n"/>
       <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
-      <c r="Q20" s="12" t="n"/>
-      <c r="R20" s="12" t="n"/>
-      <c r="S20" s="12" t="n"/>
+      <c r="N20" s="14" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="14" t="n"/>
+      <c r="Q20" s="14" t="n"/>
+      <c r="R20" s="16" t="n"/>
+      <c r="S20" s="16" t="n"/>
       <c r="T20" s="12" t="n"/>
+      <c r="U20" s="12" t="n"/>
+      <c r="V20" s="12" t="n"/>
+      <c r="W20" s="12" t="n"/>
+      <c r="X20" s="12" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>교육위원회</t>
         </is>
       </c>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>행정운영</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>임명직</t>
         </is>
       </c>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="18" t="n"/>
-      <c r="L21" s="18" t="n"/>
-      <c r="M21" s="19" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="17" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="20" t="n"/>
       <c r="N21" s="19" t="n"/>
-      <c r="O21" s="17" t="n"/>
-      <c r="P21" s="17" t="n"/>
-      <c r="Q21" s="17" t="n"/>
-      <c r="R21" s="17" t="n"/>
-      <c r="S21" s="17" t="n"/>
-      <c r="T21" s="17" t="n"/>
+      <c r="O21" s="20" t="n"/>
+      <c r="P21" s="19" t="n"/>
+      <c r="Q21" s="19" t="n"/>
+      <c r="R21" s="21" t="n"/>
+      <c r="S21" s="21" t="n"/>
+      <c r="T21" s="18" t="n"/>
+      <c r="U21" s="18" t="n"/>
+      <c r="V21" s="18" t="n"/>
+      <c r="W21" s="18" t="n"/>
+      <c r="X21" s="18" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -1705,13 +1814,17 @@
       <c r="K22" s="14" t="n"/>
       <c r="L22" s="14" t="n"/>
       <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="12" t="n"/>
-      <c r="R22" s="12" t="n"/>
-      <c r="S22" s="12" t="n"/>
+      <c r="N22" s="14" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="14" t="n"/>
+      <c r="Q22" s="14" t="n"/>
+      <c r="R22" s="16" t="n"/>
+      <c r="S22" s="16" t="n"/>
       <c r="T22" s="12" t="n"/>
+      <c r="U22" s="12" t="n"/>
+      <c r="V22" s="12" t="n"/>
+      <c r="W22" s="12" t="n"/>
+      <c r="X22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -1741,13 +1854,17 @@
       <c r="K23" s="14" t="n"/>
       <c r="L23" s="14" t="n"/>
       <c r="M23" s="15" t="n"/>
-      <c r="N23" s="15" t="n"/>
-      <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="12" t="n"/>
-      <c r="R23" s="12" t="n"/>
-      <c r="S23" s="12" t="n"/>
+      <c r="N23" s="14" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="14" t="n"/>
+      <c r="Q23" s="14" t="n"/>
+      <c r="R23" s="16" t="n"/>
+      <c r="S23" s="16" t="n"/>
       <c r="T23" s="12" t="n"/>
+      <c r="U23" s="12" t="n"/>
+      <c r="V23" s="12" t="n"/>
+      <c r="W23" s="12" t="n"/>
+      <c r="X23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -1777,13 +1894,17 @@
       <c r="K24" s="14" t="n"/>
       <c r="L24" s="14" t="n"/>
       <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="12" t="n"/>
-      <c r="R24" s="12" t="n"/>
-      <c r="S24" s="12" t="n"/>
+      <c r="N24" s="14" t="n"/>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="14" t="n"/>
+      <c r="Q24" s="14" t="n"/>
+      <c r="R24" s="16" t="n"/>
+      <c r="S24" s="16" t="n"/>
       <c r="T24" s="12" t="n"/>
+      <c r="U24" s="12" t="n"/>
+      <c r="V24" s="12" t="n"/>
+      <c r="W24" s="12" t="n"/>
+      <c r="X24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -1813,13 +1934,17 @@
       <c r="K25" s="14" t="n"/>
       <c r="L25" s="14" t="n"/>
       <c r="M25" s="15" t="n"/>
-      <c r="N25" s="15" t="n"/>
-      <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="12" t="n"/>
-      <c r="R25" s="12" t="n"/>
-      <c r="S25" s="12" t="n"/>
+      <c r="N25" s="14" t="n"/>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="14" t="n"/>
+      <c r="Q25" s="14" t="n"/>
+      <c r="R25" s="16" t="n"/>
+      <c r="S25" s="16" t="n"/>
       <c r="T25" s="12" t="n"/>
+      <c r="U25" s="12" t="n"/>
+      <c r="V25" s="12" t="n"/>
+      <c r="W25" s="12" t="n"/>
+      <c r="X25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
@@ -1849,13 +1974,17 @@
       <c r="K26" s="14" t="n"/>
       <c r="L26" s="14" t="n"/>
       <c r="M26" s="15" t="n"/>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="12" t="n"/>
-      <c r="R26" s="12" t="n"/>
-      <c r="S26" s="12" t="n"/>
+      <c r="N26" s="14" t="n"/>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="14" t="n"/>
+      <c r="Q26" s="14" t="n"/>
+      <c r="R26" s="16" t="n"/>
+      <c r="S26" s="16" t="n"/>
       <c r="T26" s="12" t="n"/>
+      <c r="U26" s="12" t="n"/>
+      <c r="V26" s="12" t="n"/>
+      <c r="W26" s="12" t="n"/>
+      <c r="X26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
@@ -1885,13 +2014,17 @@
       <c r="K27" s="14" t="n"/>
       <c r="L27" s="14" t="n"/>
       <c r="M27" s="15" t="n"/>
-      <c r="N27" s="15" t="n"/>
-      <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="12" t="n"/>
-      <c r="R27" s="12" t="n"/>
-      <c r="S27" s="12" t="n"/>
+      <c r="N27" s="14" t="n"/>
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="14" t="n"/>
+      <c r="Q27" s="14" t="n"/>
+      <c r="R27" s="16" t="n"/>
+      <c r="S27" s="16" t="n"/>
       <c r="T27" s="12" t="n"/>
+      <c r="U27" s="12" t="n"/>
+      <c r="V27" s="12" t="n"/>
+      <c r="W27" s="12" t="n"/>
+      <c r="X27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
@@ -1921,13 +2054,17 @@
       <c r="K28" s="14" t="n"/>
       <c r="L28" s="14" t="n"/>
       <c r="M28" s="15" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="12" t="n"/>
-      <c r="R28" s="12" t="n"/>
-      <c r="S28" s="12" t="n"/>
+      <c r="N28" s="14" t="n"/>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="14" t="n"/>
+      <c r="Q28" s="14" t="n"/>
+      <c r="R28" s="16" t="n"/>
+      <c r="S28" s="16" t="n"/>
       <c r="T28" s="12" t="n"/>
+      <c r="U28" s="12" t="n"/>
+      <c r="V28" s="12" t="n"/>
+      <c r="W28" s="12" t="n"/>
+      <c r="X28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n">
@@ -1957,13 +2094,17 @@
       <c r="K29" s="14" t="n"/>
       <c r="L29" s="14" t="n"/>
       <c r="M29" s="15" t="n"/>
-      <c r="N29" s="15" t="n"/>
-      <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="12" t="n"/>
-      <c r="R29" s="12" t="n"/>
-      <c r="S29" s="12" t="n"/>
+      <c r="N29" s="14" t="n"/>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="14" t="n"/>
+      <c r="Q29" s="14" t="n"/>
+      <c r="R29" s="16" t="n"/>
+      <c r="S29" s="16" t="n"/>
       <c r="T29" s="12" t="n"/>
+      <c r="U29" s="12" t="n"/>
+      <c r="V29" s="12" t="n"/>
+      <c r="W29" s="12" t="n"/>
+      <c r="X29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="n">
@@ -1993,13 +2134,17 @@
       <c r="K30" s="14" t="n"/>
       <c r="L30" s="14" t="n"/>
       <c r="M30" s="15" t="n"/>
-      <c r="N30" s="15" t="n"/>
-      <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="12" t="n"/>
-      <c r="R30" s="12" t="n"/>
-      <c r="S30" s="12" t="n"/>
+      <c r="N30" s="14" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="14" t="n"/>
+      <c r="Q30" s="14" t="n"/>
+      <c r="R30" s="16" t="n"/>
+      <c r="S30" s="16" t="n"/>
       <c r="T30" s="12" t="n"/>
+      <c r="U30" s="12" t="n"/>
+      <c r="V30" s="12" t="n"/>
+      <c r="W30" s="12" t="n"/>
+      <c r="X30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="n">
@@ -2029,13 +2174,17 @@
       <c r="K31" s="14" t="n"/>
       <c r="L31" s="14" t="n"/>
       <c r="M31" s="15" t="n"/>
-      <c r="N31" s="15" t="n"/>
-      <c r="O31" s="12" t="n"/>
-      <c r="P31" s="12" t="n"/>
-      <c r="Q31" s="12" t="n"/>
-      <c r="R31" s="12" t="n"/>
-      <c r="S31" s="12" t="n"/>
+      <c r="N31" s="14" t="n"/>
+      <c r="O31" s="15" t="n"/>
+      <c r="P31" s="14" t="n"/>
+      <c r="Q31" s="14" t="n"/>
+      <c r="R31" s="16" t="n"/>
+      <c r="S31" s="16" t="n"/>
       <c r="T31" s="12" t="n"/>
+      <c r="U31" s="12" t="n"/>
+      <c r="V31" s="12" t="n"/>
+      <c r="W31" s="12" t="n"/>
+      <c r="X31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="n">
@@ -2065,13 +2214,17 @@
       <c r="K32" s="14" t="n"/>
       <c r="L32" s="14" t="n"/>
       <c r="M32" s="15" t="n"/>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12" t="n"/>
-      <c r="Q32" s="12" t="n"/>
-      <c r="R32" s="12" t="n"/>
-      <c r="S32" s="12" t="n"/>
+      <c r="N32" s="14" t="n"/>
+      <c r="O32" s="15" t="n"/>
+      <c r="P32" s="14" t="n"/>
+      <c r="Q32" s="14" t="n"/>
+      <c r="R32" s="16" t="n"/>
+      <c r="S32" s="16" t="n"/>
       <c r="T32" s="12" t="n"/>
+      <c r="U32" s="12" t="n"/>
+      <c r="V32" s="12" t="n"/>
+      <c r="W32" s="12" t="n"/>
+      <c r="X32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n">
@@ -2101,13 +2254,17 @@
       <c r="K33" s="14" t="n"/>
       <c r="L33" s="14" t="n"/>
       <c r="M33" s="15" t="n"/>
-      <c r="N33" s="15" t="n"/>
-      <c r="O33" s="12" t="n"/>
-      <c r="P33" s="12" t="n"/>
-      <c r="Q33" s="12" t="n"/>
-      <c r="R33" s="12" t="n"/>
-      <c r="S33" s="12" t="n"/>
+      <c r="N33" s="14" t="n"/>
+      <c r="O33" s="15" t="n"/>
+      <c r="P33" s="14" t="n"/>
+      <c r="Q33" s="14" t="n"/>
+      <c r="R33" s="16" t="n"/>
+      <c r="S33" s="16" t="n"/>
       <c r="T33" s="12" t="n"/>
+      <c r="U33" s="12" t="n"/>
+      <c r="V33" s="12" t="n"/>
+      <c r="W33" s="12" t="n"/>
+      <c r="X33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="n">
@@ -2137,13 +2294,17 @@
       <c r="K34" s="14" t="n"/>
       <c r="L34" s="14" t="n"/>
       <c r="M34" s="15" t="n"/>
-      <c r="N34" s="15" t="n"/>
-      <c r="O34" s="12" t="n"/>
-      <c r="P34" s="12" t="n"/>
-      <c r="Q34" s="12" t="n"/>
-      <c r="R34" s="12" t="n"/>
-      <c r="S34" s="12" t="n"/>
+      <c r="N34" s="14" t="n"/>
+      <c r="O34" s="15" t="n"/>
+      <c r="P34" s="14" t="n"/>
+      <c r="Q34" s="14" t="n"/>
+      <c r="R34" s="16" t="n"/>
+      <c r="S34" s="16" t="n"/>
       <c r="T34" s="12" t="n"/>
+      <c r="U34" s="12" t="n"/>
+      <c r="V34" s="12" t="n"/>
+      <c r="W34" s="12" t="n"/>
+      <c r="X34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n">
@@ -2173,13 +2334,17 @@
       <c r="K35" s="14" t="n"/>
       <c r="L35" s="14" t="n"/>
       <c r="M35" s="15" t="n"/>
-      <c r="N35" s="15" t="n"/>
-      <c r="O35" s="12" t="n"/>
-      <c r="P35" s="12" t="n"/>
-      <c r="Q35" s="12" t="n"/>
-      <c r="R35" s="12" t="n"/>
-      <c r="S35" s="12" t="n"/>
+      <c r="N35" s="14" t="n"/>
+      <c r="O35" s="15" t="n"/>
+      <c r="P35" s="14" t="n"/>
+      <c r="Q35" s="14" t="n"/>
+      <c r="R35" s="16" t="n"/>
+      <c r="S35" s="16" t="n"/>
       <c r="T35" s="12" t="n"/>
+      <c r="U35" s="12" t="n"/>
+      <c r="V35" s="12" t="n"/>
+      <c r="W35" s="12" t="n"/>
+      <c r="X35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n">
@@ -2209,13 +2374,17 @@
       <c r="K36" s="14" t="n"/>
       <c r="L36" s="14" t="n"/>
       <c r="M36" s="15" t="n"/>
-      <c r="N36" s="15" t="n"/>
-      <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="12" t="n"/>
-      <c r="R36" s="12" t="n"/>
-      <c r="S36" s="12" t="n"/>
+      <c r="N36" s="14" t="n"/>
+      <c r="O36" s="15" t="n"/>
+      <c r="P36" s="14" t="n"/>
+      <c r="Q36" s="14" t="n"/>
+      <c r="R36" s="16" t="n"/>
+      <c r="S36" s="16" t="n"/>
       <c r="T36" s="12" t="n"/>
+      <c r="U36" s="12" t="n"/>
+      <c r="V36" s="12" t="n"/>
+      <c r="W36" s="12" t="n"/>
+      <c r="X36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n">
@@ -2245,13 +2414,17 @@
       <c r="K37" s="14" t="n"/>
       <c r="L37" s="14" t="n"/>
       <c r="M37" s="15" t="n"/>
-      <c r="N37" s="15" t="n"/>
-      <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="12" t="n"/>
-      <c r="R37" s="12" t="n"/>
-      <c r="S37" s="12" t="n"/>
+      <c r="N37" s="14" t="n"/>
+      <c r="O37" s="15" t="n"/>
+      <c r="P37" s="14" t="n"/>
+      <c r="Q37" s="14" t="n"/>
+      <c r="R37" s="16" t="n"/>
+      <c r="S37" s="16" t="n"/>
       <c r="T37" s="12" t="n"/>
+      <c r="U37" s="12" t="n"/>
+      <c r="V37" s="12" t="n"/>
+      <c r="W37" s="12" t="n"/>
+      <c r="X37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="9" t="n">
@@ -2281,13 +2454,17 @@
       <c r="K38" s="14" t="n"/>
       <c r="L38" s="14" t="n"/>
       <c r="M38" s="15" t="n"/>
-      <c r="N38" s="15" t="n"/>
-      <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="12" t="n"/>
-      <c r="R38" s="12" t="n"/>
-      <c r="S38" s="12" t="n"/>
+      <c r="N38" s="14" t="n"/>
+      <c r="O38" s="15" t="n"/>
+      <c r="P38" s="14" t="n"/>
+      <c r="Q38" s="14" t="n"/>
+      <c r="R38" s="16" t="n"/>
+      <c r="S38" s="16" t="n"/>
       <c r="T38" s="12" t="n"/>
+      <c r="U38" s="12" t="n"/>
+      <c r="V38" s="12" t="n"/>
+      <c r="W38" s="12" t="n"/>
+      <c r="X38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="n">
@@ -2317,13 +2494,17 @@
       <c r="K39" s="14" t="n"/>
       <c r="L39" s="14" t="n"/>
       <c r="M39" s="15" t="n"/>
-      <c r="N39" s="15" t="n"/>
-      <c r="O39" s="12" t="n"/>
-      <c r="P39" s="12" t="n"/>
-      <c r="Q39" s="12" t="n"/>
-      <c r="R39" s="12" t="n"/>
-      <c r="S39" s="12" t="n"/>
+      <c r="N39" s="14" t="n"/>
+      <c r="O39" s="15" t="n"/>
+      <c r="P39" s="14" t="n"/>
+      <c r="Q39" s="14" t="n"/>
+      <c r="R39" s="16" t="n"/>
+      <c r="S39" s="16" t="n"/>
       <c r="T39" s="12" t="n"/>
+      <c r="U39" s="12" t="n"/>
+      <c r="V39" s="12" t="n"/>
+      <c r="W39" s="12" t="n"/>
+      <c r="X39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="9" t="n">
@@ -2353,13 +2534,17 @@
       <c r="K40" s="14" t="n"/>
       <c r="L40" s="14" t="n"/>
       <c r="M40" s="15" t="n"/>
-      <c r="N40" s="15" t="n"/>
-      <c r="O40" s="12" t="n"/>
-      <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="12" t="n"/>
-      <c r="R40" s="12" t="n"/>
-      <c r="S40" s="12" t="n"/>
+      <c r="N40" s="14" t="n"/>
+      <c r="O40" s="15" t="n"/>
+      <c r="P40" s="14" t="n"/>
+      <c r="Q40" s="14" t="n"/>
+      <c r="R40" s="16" t="n"/>
+      <c r="S40" s="16" t="n"/>
       <c r="T40" s="12" t="n"/>
+      <c r="U40" s="12" t="n"/>
+      <c r="V40" s="12" t="n"/>
+      <c r="W40" s="12" t="n"/>
+      <c r="X40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n">
@@ -2389,13 +2574,17 @@
       <c r="K41" s="14" t="n"/>
       <c r="L41" s="14" t="n"/>
       <c r="M41" s="15" t="n"/>
-      <c r="N41" s="15" t="n"/>
-      <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="12" t="n"/>
-      <c r="R41" s="12" t="n"/>
-      <c r="S41" s="12" t="n"/>
+      <c r="N41" s="14" t="n"/>
+      <c r="O41" s="15" t="n"/>
+      <c r="P41" s="14" t="n"/>
+      <c r="Q41" s="14" t="n"/>
+      <c r="R41" s="16" t="n"/>
+      <c r="S41" s="16" t="n"/>
       <c r="T41" s="12" t="n"/>
+      <c r="U41" s="12" t="n"/>
+      <c r="V41" s="12" t="n"/>
+      <c r="W41" s="12" t="n"/>
+      <c r="X41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="n">
@@ -2425,13 +2614,17 @@
       <c r="K42" s="14" t="n"/>
       <c r="L42" s="14" t="n"/>
       <c r="M42" s="15" t="n"/>
-      <c r="N42" s="15" t="n"/>
-      <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
-      <c r="Q42" s="12" t="n"/>
-      <c r="R42" s="12" t="n"/>
-      <c r="S42" s="12" t="n"/>
+      <c r="N42" s="14" t="n"/>
+      <c r="O42" s="15" t="n"/>
+      <c r="P42" s="14" t="n"/>
+      <c r="Q42" s="14" t="n"/>
+      <c r="R42" s="16" t="n"/>
+      <c r="S42" s="16" t="n"/>
       <c r="T42" s="12" t="n"/>
+      <c r="U42" s="12" t="n"/>
+      <c r="V42" s="12" t="n"/>
+      <c r="W42" s="12" t="n"/>
+      <c r="X42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="9" t="n">
@@ -2461,13 +2654,17 @@
       <c r="K43" s="14" t="n"/>
       <c r="L43" s="14" t="n"/>
       <c r="M43" s="15" t="n"/>
-      <c r="N43" s="15" t="n"/>
-      <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="12" t="n"/>
-      <c r="R43" s="12" t="n"/>
-      <c r="S43" s="12" t="n"/>
+      <c r="N43" s="14" t="n"/>
+      <c r="O43" s="15" t="n"/>
+      <c r="P43" s="14" t="n"/>
+      <c r="Q43" s="14" t="n"/>
+      <c r="R43" s="16" t="n"/>
+      <c r="S43" s="16" t="n"/>
       <c r="T43" s="12" t="n"/>
+      <c r="U43" s="12" t="n"/>
+      <c r="V43" s="12" t="n"/>
+      <c r="W43" s="12" t="n"/>
+      <c r="X43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n">
@@ -2497,13 +2694,17 @@
       <c r="K44" s="14" t="n"/>
       <c r="L44" s="14" t="n"/>
       <c r="M44" s="15" t="n"/>
-      <c r="N44" s="15" t="n"/>
-      <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="12" t="n"/>
-      <c r="R44" s="12" t="n"/>
-      <c r="S44" s="12" t="n"/>
+      <c r="N44" s="14" t="n"/>
+      <c r="O44" s="15" t="n"/>
+      <c r="P44" s="14" t="n"/>
+      <c r="Q44" s="14" t="n"/>
+      <c r="R44" s="16" t="n"/>
+      <c r="S44" s="16" t="n"/>
       <c r="T44" s="12" t="n"/>
+      <c r="U44" s="12" t="n"/>
+      <c r="V44" s="12" t="n"/>
+      <c r="W44" s="12" t="n"/>
+      <c r="X44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="9" t="n">
@@ -2533,13 +2734,17 @@
       <c r="K45" s="14" t="n"/>
       <c r="L45" s="14" t="n"/>
       <c r="M45" s="15" t="n"/>
-      <c r="N45" s="15" t="n"/>
-      <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
-      <c r="Q45" s="12" t="n"/>
-      <c r="R45" s="12" t="n"/>
-      <c r="S45" s="12" t="n"/>
+      <c r="N45" s="14" t="n"/>
+      <c r="O45" s="15" t="n"/>
+      <c r="P45" s="14" t="n"/>
+      <c r="Q45" s="14" t="n"/>
+      <c r="R45" s="16" t="n"/>
+      <c r="S45" s="16" t="n"/>
       <c r="T45" s="12" t="n"/>
+      <c r="U45" s="12" t="n"/>
+      <c r="V45" s="12" t="n"/>
+      <c r="W45" s="12" t="n"/>
+      <c r="X45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="9" t="n">
@@ -2569,13 +2774,17 @@
       <c r="K46" s="14" t="n"/>
       <c r="L46" s="14" t="n"/>
       <c r="M46" s="15" t="n"/>
-      <c r="N46" s="15" t="n"/>
-      <c r="O46" s="12" t="n"/>
-      <c r="P46" s="12" t="n"/>
-      <c r="Q46" s="12" t="n"/>
-      <c r="R46" s="12" t="n"/>
-      <c r="S46" s="12" t="n"/>
+      <c r="N46" s="14" t="n"/>
+      <c r="O46" s="15" t="n"/>
+      <c r="P46" s="14" t="n"/>
+      <c r="Q46" s="14" t="n"/>
+      <c r="R46" s="16" t="n"/>
+      <c r="S46" s="16" t="n"/>
       <c r="T46" s="12" t="n"/>
+      <c r="U46" s="12" t="n"/>
+      <c r="V46" s="12" t="n"/>
+      <c r="W46" s="12" t="n"/>
+      <c r="X46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="9" t="n">
@@ -2605,13 +2814,17 @@
       <c r="K47" s="14" t="n"/>
       <c r="L47" s="14" t="n"/>
       <c r="M47" s="15" t="n"/>
-      <c r="N47" s="15" t="n"/>
-      <c r="O47" s="12" t="n"/>
-      <c r="P47" s="12" t="n"/>
-      <c r="Q47" s="12" t="n"/>
-      <c r="R47" s="12" t="n"/>
-      <c r="S47" s="12" t="n"/>
+      <c r="N47" s="14" t="n"/>
+      <c r="O47" s="15" t="n"/>
+      <c r="P47" s="14" t="n"/>
+      <c r="Q47" s="14" t="n"/>
+      <c r="R47" s="16" t="n"/>
+      <c r="S47" s="16" t="n"/>
       <c r="T47" s="12" t="n"/>
+      <c r="U47" s="12" t="n"/>
+      <c r="V47" s="12" t="n"/>
+      <c r="W47" s="12" t="n"/>
+      <c r="X47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="n">
@@ -2641,89 +2854,101 @@
       <c r="K48" s="14" t="n"/>
       <c r="L48" s="14" t="n"/>
       <c r="M48" s="15" t="n"/>
-      <c r="N48" s="15" t="n"/>
-      <c r="O48" s="12" t="n"/>
-      <c r="P48" s="12" t="n"/>
-      <c r="Q48" s="12" t="n"/>
-      <c r="R48" s="12" t="n"/>
-      <c r="S48" s="12" t="n"/>
+      <c r="N48" s="14" t="n"/>
+      <c r="O48" s="15" t="n"/>
+      <c r="P48" s="14" t="n"/>
+      <c r="Q48" s="14" t="n"/>
+      <c r="R48" s="16" t="n"/>
+      <c r="S48" s="16" t="n"/>
       <c r="T48" s="12" t="n"/>
+      <c r="U48" s="12" t="n"/>
+      <c r="V48" s="12" t="n"/>
+      <c r="W48" s="12" t="n"/>
+      <c r="X48" s="12" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n">
+      <c r="A49" s="17" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>예배부</t>
         </is>
       </c>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>성찬예식</t>
         </is>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>임명직</t>
         </is>
       </c>
-      <c r="F49" s="17" t="n"/>
-      <c r="G49" s="17" t="n"/>
-      <c r="H49" s="17" t="n"/>
-      <c r="I49" s="16" t="n"/>
-      <c r="J49" s="18" t="n"/>
-      <c r="K49" s="18" t="n"/>
-      <c r="L49" s="18" t="n"/>
-      <c r="M49" s="19" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="18" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="19" t="n"/>
+      <c r="K49" s="19" t="n"/>
+      <c r="L49" s="19" t="n"/>
+      <c r="M49" s="20" t="n"/>
       <c r="N49" s="19" t="n"/>
-      <c r="O49" s="17" t="n"/>
-      <c r="P49" s="17" t="n"/>
-      <c r="Q49" s="17" t="n"/>
-      <c r="R49" s="17" t="n"/>
-      <c r="S49" s="17" t="n"/>
-      <c r="T49" s="17" t="n"/>
+      <c r="O49" s="20" t="n"/>
+      <c r="P49" s="19" t="n"/>
+      <c r="Q49" s="19" t="n"/>
+      <c r="R49" s="21" t="n"/>
+      <c r="S49" s="21" t="n"/>
+      <c r="T49" s="18" t="n"/>
+      <c r="U49" s="18" t="n"/>
+      <c r="V49" s="18" t="n"/>
+      <c r="W49" s="18" t="n"/>
+      <c r="X49" s="18" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="n">
+      <c r="A50" s="22" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B50" s="22" t="inlineStr">
         <is>
           <t>예배부</t>
         </is>
       </c>
-      <c r="C50" s="20" t="n"/>
-      <c r="D50" s="21" t="inlineStr">
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="23" t="inlineStr">
         <is>
           <t>회계</t>
         </is>
       </c>
-      <c r="E50" s="20" t="inlineStr">
+      <c r="E50" s="22" t="inlineStr">
         <is>
           <t>임명직</t>
         </is>
       </c>
-      <c r="F50" s="21" t="n"/>
-      <c r="G50" s="21" t="inlineStr">
+      <c r="F50" s="23" t="n"/>
+      <c r="G50" s="23" t="inlineStr">
         <is>
           <t>조직표에는 회계(최현희)가 있으나 신청서 양식에는 없음 — 임명직인지, 신청서 누락인지 확인 필요</t>
         </is>
       </c>
-      <c r="H50" s="21" t="n"/>
-      <c r="I50" s="20" t="n"/>
-      <c r="J50" s="22" t="n"/>
-      <c r="K50" s="22" t="n"/>
-      <c r="L50" s="22" t="n"/>
-      <c r="M50" s="23" t="n"/>
-      <c r="N50" s="23" t="n"/>
-      <c r="O50" s="21" t="n"/>
-      <c r="P50" s="21" t="n"/>
-      <c r="Q50" s="21" t="n"/>
-      <c r="R50" s="21" t="n"/>
-      <c r="S50" s="21" t="n"/>
-      <c r="T50" s="21" t="n"/>
+      <c r="H50" s="23" t="n"/>
+      <c r="I50" s="22" t="n"/>
+      <c r="J50" s="24" t="n"/>
+      <c r="K50" s="24" t="n"/>
+      <c r="L50" s="24" t="n"/>
+      <c r="M50" s="25" t="n"/>
+      <c r="N50" s="24" t="n"/>
+      <c r="O50" s="25" t="n"/>
+      <c r="P50" s="24" t="n"/>
+      <c r="Q50" s="24" t="n"/>
+      <c r="R50" s="26" t="n"/>
+      <c r="S50" s="26" t="n"/>
+      <c r="T50" s="23" t="n"/>
+      <c r="U50" s="23" t="n"/>
+      <c r="V50" s="23" t="n"/>
+      <c r="W50" s="23" t="n"/>
+      <c r="X50" s="23" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="n">
@@ -2753,13 +2978,17 @@
       <c r="K51" s="14" t="n"/>
       <c r="L51" s="14" t="n"/>
       <c r="M51" s="15" t="n"/>
-      <c r="N51" s="15" t="n"/>
-      <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
-      <c r="Q51" s="12" t="n"/>
-      <c r="R51" s="12" t="n"/>
-      <c r="S51" s="12" t="n"/>
+      <c r="N51" s="14" t="n"/>
+      <c r="O51" s="15" t="n"/>
+      <c r="P51" s="14" t="n"/>
+      <c r="Q51" s="14" t="n"/>
+      <c r="R51" s="16" t="n"/>
+      <c r="S51" s="16" t="n"/>
       <c r="T51" s="12" t="n"/>
+      <c r="U51" s="12" t="n"/>
+      <c r="V51" s="12" t="n"/>
+      <c r="W51" s="12" t="n"/>
+      <c r="X51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="9" t="n">
@@ -2789,13 +3018,17 @@
       <c r="K52" s="14" t="n"/>
       <c r="L52" s="14" t="n"/>
       <c r="M52" s="15" t="n"/>
-      <c r="N52" s="15" t="n"/>
-      <c r="O52" s="12" t="n"/>
-      <c r="P52" s="12" t="n"/>
-      <c r="Q52" s="12" t="n"/>
-      <c r="R52" s="12" t="n"/>
-      <c r="S52" s="12" t="n"/>
+      <c r="N52" s="14" t="n"/>
+      <c r="O52" s="15" t="n"/>
+      <c r="P52" s="14" t="n"/>
+      <c r="Q52" s="14" t="n"/>
+      <c r="R52" s="16" t="n"/>
+      <c r="S52" s="16" t="n"/>
       <c r="T52" s="12" t="n"/>
+      <c r="U52" s="12" t="n"/>
+      <c r="V52" s="12" t="n"/>
+      <c r="W52" s="12" t="n"/>
+      <c r="X52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n">
@@ -2825,13 +3058,17 @@
       <c r="K53" s="14" t="n"/>
       <c r="L53" s="14" t="n"/>
       <c r="M53" s="15" t="n"/>
-      <c r="N53" s="15" t="n"/>
-      <c r="O53" s="12" t="n"/>
-      <c r="P53" s="12" t="n"/>
-      <c r="Q53" s="12" t="n"/>
-      <c r="R53" s="12" t="n"/>
-      <c r="S53" s="12" t="n"/>
+      <c r="N53" s="14" t="n"/>
+      <c r="O53" s="15" t="n"/>
+      <c r="P53" s="14" t="n"/>
+      <c r="Q53" s="14" t="n"/>
+      <c r="R53" s="16" t="n"/>
+      <c r="S53" s="16" t="n"/>
       <c r="T53" s="12" t="n"/>
+      <c r="U53" s="12" t="n"/>
+      <c r="V53" s="12" t="n"/>
+      <c r="W53" s="12" t="n"/>
+      <c r="X53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="9" t="n">
@@ -2861,13 +3098,17 @@
       <c r="K54" s="14" t="n"/>
       <c r="L54" s="14" t="n"/>
       <c r="M54" s="15" t="n"/>
-      <c r="N54" s="15" t="n"/>
-      <c r="O54" s="12" t="n"/>
-      <c r="P54" s="12" t="n"/>
-      <c r="Q54" s="12" t="n"/>
-      <c r="R54" s="12" t="n"/>
-      <c r="S54" s="12" t="n"/>
+      <c r="N54" s="14" t="n"/>
+      <c r="O54" s="15" t="n"/>
+      <c r="P54" s="14" t="n"/>
+      <c r="Q54" s="14" t="n"/>
+      <c r="R54" s="16" t="n"/>
+      <c r="S54" s="16" t="n"/>
       <c r="T54" s="12" t="n"/>
+      <c r="U54" s="12" t="n"/>
+      <c r="V54" s="12" t="n"/>
+      <c r="W54" s="12" t="n"/>
+      <c r="X54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="9" t="n">
@@ -2897,13 +3138,17 @@
       <c r="K55" s="14" t="n"/>
       <c r="L55" s="14" t="n"/>
       <c r="M55" s="15" t="n"/>
-      <c r="N55" s="15" t="n"/>
-      <c r="O55" s="12" t="n"/>
-      <c r="P55" s="12" t="n"/>
-      <c r="Q55" s="12" t="n"/>
-      <c r="R55" s="12" t="n"/>
-      <c r="S55" s="12" t="n"/>
+      <c r="N55" s="14" t="n"/>
+      <c r="O55" s="15" t="n"/>
+      <c r="P55" s="14" t="n"/>
+      <c r="Q55" s="14" t="n"/>
+      <c r="R55" s="16" t="n"/>
+      <c r="S55" s="16" t="n"/>
       <c r="T55" s="12" t="n"/>
+      <c r="U55" s="12" t="n"/>
+      <c r="V55" s="12" t="n"/>
+      <c r="W55" s="12" t="n"/>
+      <c r="X55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
@@ -2933,13 +3178,17 @@
       <c r="K56" s="14" t="n"/>
       <c r="L56" s="14" t="n"/>
       <c r="M56" s="15" t="n"/>
-      <c r="N56" s="15" t="n"/>
-      <c r="O56" s="12" t="n"/>
-      <c r="P56" s="12" t="n"/>
-      <c r="Q56" s="12" t="n"/>
-      <c r="R56" s="12" t="n"/>
-      <c r="S56" s="12" t="n"/>
+      <c r="N56" s="14" t="n"/>
+      <c r="O56" s="15" t="n"/>
+      <c r="P56" s="14" t="n"/>
+      <c r="Q56" s="14" t="n"/>
+      <c r="R56" s="16" t="n"/>
+      <c r="S56" s="16" t="n"/>
       <c r="T56" s="12" t="n"/>
+      <c r="U56" s="12" t="n"/>
+      <c r="V56" s="12" t="n"/>
+      <c r="W56" s="12" t="n"/>
+      <c r="X56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
@@ -2969,13 +3218,17 @@
       <c r="K57" s="14" t="n"/>
       <c r="L57" s="14" t="n"/>
       <c r="M57" s="15" t="n"/>
-      <c r="N57" s="15" t="n"/>
-      <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
-      <c r="Q57" s="12" t="n"/>
-      <c r="R57" s="12" t="n"/>
-      <c r="S57" s="12" t="n"/>
+      <c r="N57" s="14" t="n"/>
+      <c r="O57" s="15" t="n"/>
+      <c r="P57" s="14" t="n"/>
+      <c r="Q57" s="14" t="n"/>
+      <c r="R57" s="16" t="n"/>
+      <c r="S57" s="16" t="n"/>
       <c r="T57" s="12" t="n"/>
+      <c r="U57" s="12" t="n"/>
+      <c r="V57" s="12" t="n"/>
+      <c r="W57" s="12" t="n"/>
+      <c r="X57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n">
@@ -3005,13 +3258,17 @@
       <c r="K58" s="14" t="n"/>
       <c r="L58" s="14" t="n"/>
       <c r="M58" s="15" t="n"/>
-      <c r="N58" s="15" t="n"/>
-      <c r="O58" s="12" t="n"/>
-      <c r="P58" s="12" t="n"/>
-      <c r="Q58" s="12" t="n"/>
-      <c r="R58" s="12" t="n"/>
-      <c r="S58" s="12" t="n"/>
+      <c r="N58" s="14" t="n"/>
+      <c r="O58" s="15" t="n"/>
+      <c r="P58" s="14" t="n"/>
+      <c r="Q58" s="14" t="n"/>
+      <c r="R58" s="16" t="n"/>
+      <c r="S58" s="16" t="n"/>
       <c r="T58" s="12" t="n"/>
+      <c r="U58" s="12" t="n"/>
+      <c r="V58" s="12" t="n"/>
+      <c r="W58" s="12" t="n"/>
+      <c r="X58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="9" t="n">
@@ -3041,13 +3298,17 @@
       <c r="K59" s="14" t="n"/>
       <c r="L59" s="14" t="n"/>
       <c r="M59" s="15" t="n"/>
-      <c r="N59" s="15" t="n"/>
-      <c r="O59" s="12" t="n"/>
-      <c r="P59" s="12" t="n"/>
-      <c r="Q59" s="12" t="n"/>
-      <c r="R59" s="12" t="n"/>
-      <c r="S59" s="12" t="n"/>
+      <c r="N59" s="14" t="n"/>
+      <c r="O59" s="15" t="n"/>
+      <c r="P59" s="14" t="n"/>
+      <c r="Q59" s="14" t="n"/>
+      <c r="R59" s="16" t="n"/>
+      <c r="S59" s="16" t="n"/>
       <c r="T59" s="12" t="n"/>
+      <c r="U59" s="12" t="n"/>
+      <c r="V59" s="12" t="n"/>
+      <c r="W59" s="12" t="n"/>
+      <c r="X59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="9" t="n">
@@ -3077,13 +3338,17 @@
       <c r="K60" s="14" t="n"/>
       <c r="L60" s="14" t="n"/>
       <c r="M60" s="15" t="n"/>
-      <c r="N60" s="15" t="n"/>
-      <c r="O60" s="12" t="n"/>
-      <c r="P60" s="12" t="n"/>
-      <c r="Q60" s="12" t="n"/>
-      <c r="R60" s="12" t="n"/>
-      <c r="S60" s="12" t="n"/>
+      <c r="N60" s="14" t="n"/>
+      <c r="O60" s="15" t="n"/>
+      <c r="P60" s="14" t="n"/>
+      <c r="Q60" s="14" t="n"/>
+      <c r="R60" s="16" t="n"/>
+      <c r="S60" s="16" t="n"/>
       <c r="T60" s="12" t="n"/>
+      <c r="U60" s="12" t="n"/>
+      <c r="V60" s="12" t="n"/>
+      <c r="W60" s="12" t="n"/>
+      <c r="X60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
@@ -3113,13 +3378,17 @@
       <c r="K61" s="14" t="n"/>
       <c r="L61" s="14" t="n"/>
       <c r="M61" s="15" t="n"/>
-      <c r="N61" s="15" t="n"/>
-      <c r="O61" s="12" t="n"/>
-      <c r="P61" s="12" t="n"/>
-      <c r="Q61" s="12" t="n"/>
-      <c r="R61" s="12" t="n"/>
-      <c r="S61" s="12" t="n"/>
+      <c r="N61" s="14" t="n"/>
+      <c r="O61" s="15" t="n"/>
+      <c r="P61" s="14" t="n"/>
+      <c r="Q61" s="14" t="n"/>
+      <c r="R61" s="16" t="n"/>
+      <c r="S61" s="16" t="n"/>
       <c r="T61" s="12" t="n"/>
+      <c r="U61" s="12" t="n"/>
+      <c r="V61" s="12" t="n"/>
+      <c r="W61" s="12" t="n"/>
+      <c r="X61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="9" t="n">
@@ -3149,13 +3418,17 @@
       <c r="K62" s="14" t="n"/>
       <c r="L62" s="14" t="n"/>
       <c r="M62" s="15" t="n"/>
-      <c r="N62" s="15" t="n"/>
-      <c r="O62" s="12" t="n"/>
-      <c r="P62" s="12" t="n"/>
-      <c r="Q62" s="12" t="n"/>
-      <c r="R62" s="12" t="n"/>
-      <c r="S62" s="12" t="n"/>
+      <c r="N62" s="14" t="n"/>
+      <c r="O62" s="15" t="n"/>
+      <c r="P62" s="14" t="n"/>
+      <c r="Q62" s="14" t="n"/>
+      <c r="R62" s="16" t="n"/>
+      <c r="S62" s="16" t="n"/>
       <c r="T62" s="12" t="n"/>
+      <c r="U62" s="12" t="n"/>
+      <c r="V62" s="12" t="n"/>
+      <c r="W62" s="12" t="n"/>
+      <c r="X62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
@@ -3185,13 +3458,17 @@
       <c r="K63" s="14" t="n"/>
       <c r="L63" s="14" t="n"/>
       <c r="M63" s="15" t="n"/>
-      <c r="N63" s="15" t="n"/>
-      <c r="O63" s="12" t="n"/>
-      <c r="P63" s="12" t="n"/>
-      <c r="Q63" s="12" t="n"/>
-      <c r="R63" s="12" t="n"/>
-      <c r="S63" s="12" t="n"/>
+      <c r="N63" s="14" t="n"/>
+      <c r="O63" s="15" t="n"/>
+      <c r="P63" s="14" t="n"/>
+      <c r="Q63" s="14" t="n"/>
+      <c r="R63" s="16" t="n"/>
+      <c r="S63" s="16" t="n"/>
       <c r="T63" s="12" t="n"/>
+      <c r="U63" s="12" t="n"/>
+      <c r="V63" s="12" t="n"/>
+      <c r="W63" s="12" t="n"/>
+      <c r="X63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="9" t="n">
@@ -3225,17 +3502,21 @@
       <c r="K64" s="14" t="n"/>
       <c r="L64" s="14" t="n"/>
       <c r="M64" s="15" t="n"/>
-      <c r="N64" s="15" t="n"/>
-      <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="inlineStr">
+      <c r="N64" s="14" t="n"/>
+      <c r="O64" s="15" t="n"/>
+      <c r="P64" s="14" t="n"/>
+      <c r="Q64" s="14" t="n"/>
+      <c r="R64" s="16" t="n"/>
+      <c r="S64" s="16" t="n"/>
+      <c r="T64" s="12" t="inlineStr">
         <is>
           <t>1부</t>
         </is>
       </c>
-      <c r="Q64" s="12" t="n"/>
-      <c r="R64" s="12" t="n"/>
-      <c r="S64" s="12" t="n"/>
-      <c r="T64" s="12" t="n"/>
+      <c r="U64" s="12" t="n"/>
+      <c r="V64" s="12" t="n"/>
+      <c r="W64" s="12" t="n"/>
+      <c r="X64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
@@ -3269,17 +3550,21 @@
       <c r="K65" s="14" t="n"/>
       <c r="L65" s="14" t="n"/>
       <c r="M65" s="15" t="n"/>
-      <c r="N65" s="15" t="n"/>
-      <c r="O65" s="12" t="n"/>
-      <c r="P65" s="12" t="inlineStr">
+      <c r="N65" s="14" t="n"/>
+      <c r="O65" s="15" t="n"/>
+      <c r="P65" s="14" t="n"/>
+      <c r="Q65" s="14" t="n"/>
+      <c r="R65" s="16" t="n"/>
+      <c r="S65" s="16" t="n"/>
+      <c r="T65" s="12" t="inlineStr">
         <is>
           <t>2부</t>
         </is>
       </c>
-      <c r="Q65" s="12" t="n"/>
-      <c r="R65" s="12" t="n"/>
-      <c r="S65" s="12" t="n"/>
-      <c r="T65" s="12" t="n"/>
+      <c r="U65" s="12" t="n"/>
+      <c r="V65" s="12" t="n"/>
+      <c r="W65" s="12" t="n"/>
+      <c r="X65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n">
@@ -3313,17 +3598,21 @@
       <c r="K66" s="14" t="n"/>
       <c r="L66" s="14" t="n"/>
       <c r="M66" s="15" t="n"/>
-      <c r="N66" s="15" t="n"/>
-      <c r="O66" s="12" t="n"/>
-      <c r="P66" s="12" t="inlineStr">
+      <c r="N66" s="14" t="n"/>
+      <c r="O66" s="15" t="n"/>
+      <c r="P66" s="14" t="n"/>
+      <c r="Q66" s="14" t="n"/>
+      <c r="R66" s="16" t="n"/>
+      <c r="S66" s="16" t="n"/>
+      <c r="T66" s="12" t="inlineStr">
         <is>
           <t>3부</t>
         </is>
       </c>
-      <c r="Q66" s="12" t="n"/>
-      <c r="R66" s="12" t="n"/>
-      <c r="S66" s="12" t="n"/>
-      <c r="T66" s="12" t="n"/>
+      <c r="U66" s="12" t="n"/>
+      <c r="V66" s="12" t="n"/>
+      <c r="W66" s="12" t="n"/>
+      <c r="X66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
@@ -3357,17 +3646,21 @@
       <c r="K67" s="14" t="n"/>
       <c r="L67" s="14" t="n"/>
       <c r="M67" s="15" t="n"/>
-      <c r="N67" s="15" t="n"/>
-      <c r="O67" s="12" t="n"/>
-      <c r="P67" s="12" t="inlineStr">
+      <c r="N67" s="14" t="n"/>
+      <c r="O67" s="15" t="n"/>
+      <c r="P67" s="14" t="n"/>
+      <c r="Q67" s="14" t="n"/>
+      <c r="R67" s="16" t="n"/>
+      <c r="S67" s="16" t="n"/>
+      <c r="T67" s="12" t="inlineStr">
         <is>
           <t>청년</t>
         </is>
       </c>
-      <c r="Q67" s="12" t="n"/>
-      <c r="R67" s="12" t="n"/>
-      <c r="S67" s="12" t="n"/>
-      <c r="T67" s="12" t="n"/>
+      <c r="U67" s="12" t="n"/>
+      <c r="V67" s="12" t="n"/>
+      <c r="W67" s="12" t="n"/>
+      <c r="X67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n">
@@ -3401,17 +3694,21 @@
       <c r="K68" s="14" t="n"/>
       <c r="L68" s="14" t="n"/>
       <c r="M68" s="15" t="n"/>
-      <c r="N68" s="15" t="n"/>
-      <c r="O68" s="12" t="n"/>
-      <c r="P68" s="12" t="inlineStr">
+      <c r="N68" s="14" t="n"/>
+      <c r="O68" s="15" t="n"/>
+      <c r="P68" s="14" t="n"/>
+      <c r="Q68" s="14" t="n"/>
+      <c r="R68" s="16" t="n"/>
+      <c r="S68" s="16" t="n"/>
+      <c r="T68" s="12" t="inlineStr">
         <is>
           <t>오후</t>
         </is>
       </c>
-      <c r="Q68" s="12" t="n"/>
-      <c r="R68" s="12" t="n"/>
-      <c r="S68" s="12" t="n"/>
-      <c r="T68" s="12" t="n"/>
+      <c r="U68" s="12" t="n"/>
+      <c r="V68" s="12" t="n"/>
+      <c r="W68" s="12" t="n"/>
+      <c r="X68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="9" t="n">
@@ -3445,13 +3742,17 @@
       <c r="K69" s="14" t="n"/>
       <c r="L69" s="14" t="n"/>
       <c r="M69" s="15" t="n"/>
-      <c r="N69" s="15" t="n"/>
-      <c r="O69" s="12" t="n"/>
-      <c r="P69" s="12" t="n"/>
-      <c r="Q69" s="12" t="n"/>
-      <c r="R69" s="12" t="n"/>
-      <c r="S69" s="12" t="n"/>
+      <c r="N69" s="14" t="n"/>
+      <c r="O69" s="15" t="n"/>
+      <c r="P69" s="14" t="n"/>
+      <c r="Q69" s="14" t="n"/>
+      <c r="R69" s="16" t="n"/>
+      <c r="S69" s="16" t="n"/>
       <c r="T69" s="12" t="n"/>
+      <c r="U69" s="12" t="n"/>
+      <c r="V69" s="12" t="n"/>
+      <c r="W69" s="12" t="n"/>
+      <c r="X69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="9" t="n">
@@ -3485,13 +3786,17 @@
       <c r="K70" s="14" t="n"/>
       <c r="L70" s="14" t="n"/>
       <c r="M70" s="15" t="n"/>
-      <c r="N70" s="15" t="n"/>
-      <c r="O70" s="12" t="n"/>
-      <c r="P70" s="12" t="n"/>
-      <c r="Q70" s="12" t="n"/>
-      <c r="R70" s="12" t="n"/>
-      <c r="S70" s="12" t="n"/>
+      <c r="N70" s="14" t="n"/>
+      <c r="O70" s="15" t="n"/>
+      <c r="P70" s="14" t="n"/>
+      <c r="Q70" s="14" t="n"/>
+      <c r="R70" s="16" t="n"/>
+      <c r="S70" s="16" t="n"/>
       <c r="T70" s="12" t="n"/>
+      <c r="U70" s="12" t="n"/>
+      <c r="V70" s="12" t="n"/>
+      <c r="W70" s="12" t="n"/>
+      <c r="X70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="9" t="n">
@@ -3525,13 +3830,17 @@
       <c r="K71" s="14" t="n"/>
       <c r="L71" s="14" t="n"/>
       <c r="M71" s="15" t="n"/>
-      <c r="N71" s="15" t="n"/>
-      <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
-      <c r="Q71" s="12" t="n"/>
-      <c r="R71" s="12" t="n"/>
-      <c r="S71" s="12" t="n"/>
+      <c r="N71" s="14" t="n"/>
+      <c r="O71" s="15" t="n"/>
+      <c r="P71" s="14" t="n"/>
+      <c r="Q71" s="14" t="n"/>
+      <c r="R71" s="16" t="n"/>
+      <c r="S71" s="16" t="n"/>
       <c r="T71" s="12" t="n"/>
+      <c r="U71" s="12" t="n"/>
+      <c r="V71" s="12" t="n"/>
+      <c r="W71" s="12" t="n"/>
+      <c r="X71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="9" t="n">
@@ -3565,13 +3874,17 @@
       <c r="K72" s="14" t="n"/>
       <c r="L72" s="14" t="n"/>
       <c r="M72" s="15" t="n"/>
-      <c r="N72" s="15" t="n"/>
-      <c r="O72" s="12" t="n"/>
-      <c r="P72" s="12" t="n"/>
-      <c r="Q72" s="12" t="n"/>
-      <c r="R72" s="12" t="n"/>
-      <c r="S72" s="12" t="n"/>
+      <c r="N72" s="14" t="n"/>
+      <c r="O72" s="15" t="n"/>
+      <c r="P72" s="14" t="n"/>
+      <c r="Q72" s="14" t="n"/>
+      <c r="R72" s="16" t="n"/>
+      <c r="S72" s="16" t="n"/>
       <c r="T72" s="12" t="n"/>
+      <c r="U72" s="12" t="n"/>
+      <c r="V72" s="12" t="n"/>
+      <c r="W72" s="12" t="n"/>
+      <c r="X72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="9" t="n">
@@ -3605,13 +3918,17 @@
       <c r="K73" s="14" t="n"/>
       <c r="L73" s="14" t="n"/>
       <c r="M73" s="15" t="n"/>
-      <c r="N73" s="15" t="n"/>
-      <c r="O73" s="12" t="n"/>
-      <c r="P73" s="12" t="n"/>
-      <c r="Q73" s="12" t="n"/>
-      <c r="R73" s="12" t="n"/>
-      <c r="S73" s="12" t="n"/>
+      <c r="N73" s="14" t="n"/>
+      <c r="O73" s="15" t="n"/>
+      <c r="P73" s="14" t="n"/>
+      <c r="Q73" s="14" t="n"/>
+      <c r="R73" s="16" t="n"/>
+      <c r="S73" s="16" t="n"/>
       <c r="T73" s="12" t="n"/>
+      <c r="U73" s="12" t="n"/>
+      <c r="V73" s="12" t="n"/>
+      <c r="W73" s="12" t="n"/>
+      <c r="X73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="n">
@@ -3645,13 +3962,17 @@
       <c r="K74" s="14" t="n"/>
       <c r="L74" s="14" t="n"/>
       <c r="M74" s="15" t="n"/>
-      <c r="N74" s="15" t="n"/>
-      <c r="O74" s="12" t="n"/>
-      <c r="P74" s="12" t="n"/>
-      <c r="Q74" s="12" t="n"/>
-      <c r="R74" s="12" t="n"/>
-      <c r="S74" s="12" t="n"/>
+      <c r="N74" s="14" t="n"/>
+      <c r="O74" s="15" t="n"/>
+      <c r="P74" s="14" t="n"/>
+      <c r="Q74" s="14" t="n"/>
+      <c r="R74" s="16" t="n"/>
+      <c r="S74" s="16" t="n"/>
       <c r="T74" s="12" t="n"/>
+      <c r="U74" s="12" t="n"/>
+      <c r="V74" s="12" t="n"/>
+      <c r="W74" s="12" t="n"/>
+      <c r="X74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="9" t="n">
@@ -3685,17 +4006,21 @@
       <c r="K75" s="14" t="n"/>
       <c r="L75" s="14" t="n"/>
       <c r="M75" s="15" t="n"/>
-      <c r="N75" s="15" t="n"/>
-      <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="inlineStr">
+      <c r="N75" s="14" t="n"/>
+      <c r="O75" s="15" t="n"/>
+      <c r="P75" s="14" t="n"/>
+      <c r="Q75" s="14" t="n"/>
+      <c r="R75" s="16" t="n"/>
+      <c r="S75" s="16" t="n"/>
+      <c r="T75" s="12" t="inlineStr">
         <is>
           <t>2부</t>
         </is>
       </c>
-      <c r="Q75" s="12" t="n"/>
-      <c r="R75" s="12" t="n"/>
-      <c r="S75" s="12" t="n"/>
-      <c r="T75" s="12" t="n"/>
+      <c r="U75" s="12" t="n"/>
+      <c r="V75" s="12" t="n"/>
+      <c r="W75" s="12" t="n"/>
+      <c r="X75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="9" t="n">
@@ -3729,17 +4054,21 @@
       <c r="K76" s="14" t="n"/>
       <c r="L76" s="14" t="n"/>
       <c r="M76" s="15" t="n"/>
-      <c r="N76" s="15" t="n"/>
-      <c r="O76" s="12" t="n"/>
-      <c r="P76" s="12" t="inlineStr">
+      <c r="N76" s="14" t="n"/>
+      <c r="O76" s="15" t="n"/>
+      <c r="P76" s="14" t="n"/>
+      <c r="Q76" s="14" t="n"/>
+      <c r="R76" s="16" t="n"/>
+      <c r="S76" s="16" t="n"/>
+      <c r="T76" s="12" t="inlineStr">
         <is>
           <t>3부</t>
         </is>
       </c>
-      <c r="Q76" s="12" t="n"/>
-      <c r="R76" s="12" t="n"/>
-      <c r="S76" s="12" t="n"/>
-      <c r="T76" s="12" t="n"/>
+      <c r="U76" s="12" t="n"/>
+      <c r="V76" s="12" t="n"/>
+      <c r="W76" s="12" t="n"/>
+      <c r="X76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
@@ -3769,13 +4098,17 @@
       <c r="K77" s="14" t="n"/>
       <c r="L77" s="14" t="n"/>
       <c r="M77" s="15" t="n"/>
-      <c r="N77" s="15" t="n"/>
-      <c r="O77" s="12" t="n"/>
-      <c r="P77" s="12" t="n"/>
-      <c r="Q77" s="12" t="n"/>
-      <c r="R77" s="12" t="n"/>
-      <c r="S77" s="12" t="n"/>
+      <c r="N77" s="14" t="n"/>
+      <c r="O77" s="15" t="n"/>
+      <c r="P77" s="14" t="n"/>
+      <c r="Q77" s="14" t="n"/>
+      <c r="R77" s="16" t="n"/>
+      <c r="S77" s="16" t="n"/>
       <c r="T77" s="12" t="n"/>
+      <c r="U77" s="12" t="n"/>
+      <c r="V77" s="12" t="n"/>
+      <c r="W77" s="12" t="n"/>
+      <c r="X77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="9" t="n">
@@ -3805,13 +4138,17 @@
       <c r="K78" s="14" t="n"/>
       <c r="L78" s="14" t="n"/>
       <c r="M78" s="15" t="n"/>
-      <c r="N78" s="15" t="n"/>
-      <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
-      <c r="Q78" s="12" t="n"/>
-      <c r="R78" s="12" t="n"/>
-      <c r="S78" s="12" t="n"/>
+      <c r="N78" s="14" t="n"/>
+      <c r="O78" s="15" t="n"/>
+      <c r="P78" s="14" t="n"/>
+      <c r="Q78" s="14" t="n"/>
+      <c r="R78" s="16" t="n"/>
+      <c r="S78" s="16" t="n"/>
       <c r="T78" s="12" t="n"/>
+      <c r="U78" s="12" t="n"/>
+      <c r="V78" s="12" t="n"/>
+      <c r="W78" s="12" t="n"/>
+      <c r="X78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="9" t="n">
@@ -3841,13 +4178,17 @@
       <c r="K79" s="14" t="n"/>
       <c r="L79" s="14" t="n"/>
       <c r="M79" s="15" t="n"/>
-      <c r="N79" s="15" t="n"/>
-      <c r="O79" s="12" t="n"/>
-      <c r="P79" s="12" t="n"/>
-      <c r="Q79" s="12" t="n"/>
-      <c r="R79" s="12" t="n"/>
-      <c r="S79" s="12" t="n"/>
+      <c r="N79" s="14" t="n"/>
+      <c r="O79" s="15" t="n"/>
+      <c r="P79" s="14" t="n"/>
+      <c r="Q79" s="14" t="n"/>
+      <c r="R79" s="16" t="n"/>
+      <c r="S79" s="16" t="n"/>
       <c r="T79" s="12" t="n"/>
+      <c r="U79" s="12" t="n"/>
+      <c r="V79" s="12" t="n"/>
+      <c r="W79" s="12" t="n"/>
+      <c r="X79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="9" t="n">
@@ -3877,13 +4218,17 @@
       <c r="K80" s="14" t="n"/>
       <c r="L80" s="14" t="n"/>
       <c r="M80" s="15" t="n"/>
-      <c r="N80" s="15" t="n"/>
-      <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
-      <c r="Q80" s="12" t="n"/>
-      <c r="R80" s="12" t="n"/>
-      <c r="S80" s="12" t="n"/>
+      <c r="N80" s="14" t="n"/>
+      <c r="O80" s="15" t="n"/>
+      <c r="P80" s="14" t="n"/>
+      <c r="Q80" s="14" t="n"/>
+      <c r="R80" s="16" t="n"/>
+      <c r="S80" s="16" t="n"/>
       <c r="T80" s="12" t="n"/>
+      <c r="U80" s="12" t="n"/>
+      <c r="V80" s="12" t="n"/>
+      <c r="W80" s="12" t="n"/>
+      <c r="X80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
@@ -3913,13 +4258,17 @@
       <c r="K81" s="14" t="n"/>
       <c r="L81" s="14" t="n"/>
       <c r="M81" s="15" t="n"/>
-      <c r="N81" s="15" t="n"/>
-      <c r="O81" s="12" t="n"/>
-      <c r="P81" s="12" t="n"/>
-      <c r="Q81" s="12" t="n"/>
-      <c r="R81" s="12" t="n"/>
-      <c r="S81" s="12" t="n"/>
+      <c r="N81" s="14" t="n"/>
+      <c r="O81" s="15" t="n"/>
+      <c r="P81" s="14" t="n"/>
+      <c r="Q81" s="14" t="n"/>
+      <c r="R81" s="16" t="n"/>
+      <c r="S81" s="16" t="n"/>
       <c r="T81" s="12" t="n"/>
+      <c r="U81" s="12" t="n"/>
+      <c r="V81" s="12" t="n"/>
+      <c r="W81" s="12" t="n"/>
+      <c r="X81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="9" t="n">
@@ -3949,13 +4298,17 @@
       <c r="K82" s="14" t="n"/>
       <c r="L82" s="14" t="n"/>
       <c r="M82" s="15" t="n"/>
-      <c r="N82" s="15" t="n"/>
-      <c r="O82" s="12" t="n"/>
-      <c r="P82" s="12" t="n"/>
-      <c r="Q82" s="12" t="n"/>
-      <c r="R82" s="12" t="n"/>
-      <c r="S82" s="12" t="n"/>
+      <c r="N82" s="14" t="n"/>
+      <c r="O82" s="15" t="n"/>
+      <c r="P82" s="14" t="n"/>
+      <c r="Q82" s="14" t="n"/>
+      <c r="R82" s="16" t="n"/>
+      <c r="S82" s="16" t="n"/>
       <c r="T82" s="12" t="n"/>
+      <c r="U82" s="12" t="n"/>
+      <c r="V82" s="12" t="n"/>
+      <c r="W82" s="12" t="n"/>
+      <c r="X82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="9" t="n">
@@ -3985,13 +4338,17 @@
       <c r="K83" s="14" t="n"/>
       <c r="L83" s="14" t="n"/>
       <c r="M83" s="15" t="n"/>
-      <c r="N83" s="15" t="n"/>
-      <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="12" t="n"/>
-      <c r="R83" s="12" t="n"/>
-      <c r="S83" s="12" t="n"/>
+      <c r="N83" s="14" t="n"/>
+      <c r="O83" s="15" t="n"/>
+      <c r="P83" s="14" t="n"/>
+      <c r="Q83" s="14" t="n"/>
+      <c r="R83" s="16" t="n"/>
+      <c r="S83" s="16" t="n"/>
       <c r="T83" s="12" t="n"/>
+      <c r="U83" s="12" t="n"/>
+      <c r="V83" s="12" t="n"/>
+      <c r="W83" s="12" t="n"/>
+      <c r="X83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="9" t="n">
@@ -4021,169 +4378,189 @@
       <c r="K84" s="14" t="n"/>
       <c r="L84" s="14" t="n"/>
       <c r="M84" s="15" t="n"/>
-      <c r="N84" s="15" t="n"/>
-      <c r="O84" s="12" t="n"/>
-      <c r="P84" s="12" t="n"/>
-      <c r="Q84" s="12" t="n"/>
-      <c r="R84" s="12" t="n"/>
-      <c r="S84" s="12" t="n"/>
+      <c r="N84" s="14" t="n"/>
+      <c r="O84" s="15" t="n"/>
+      <c r="P84" s="14" t="n"/>
+      <c r="Q84" s="14" t="n"/>
+      <c r="R84" s="16" t="n"/>
+      <c r="S84" s="16" t="n"/>
       <c r="T84" s="12" t="n"/>
+      <c r="U84" s="12" t="n"/>
+      <c r="V84" s="12" t="n"/>
+      <c r="W84" s="12" t="n"/>
+      <c r="X84" s="12" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="n">
+      <c r="A85" s="22" t="n">
         <v>83</v>
       </c>
-      <c r="B85" s="20" t="inlineStr">
+      <c r="B85" s="22" t="inlineStr">
         <is>
           <t>L-12(목양부)</t>
         </is>
       </c>
-      <c r="C85" s="20" t="n"/>
-      <c r="D85" s="21" t="inlineStr">
+      <c r="C85" s="22" t="n"/>
+      <c r="D85" s="23" t="inlineStr">
         <is>
           <t>정착관리</t>
         </is>
       </c>
-      <c r="E85" s="20" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F85" s="21" t="n"/>
-      <c r="G85" s="21" t="inlineStr">
+      <c r="E85" s="22" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="n"/>
+      <c r="G85" s="23" t="inlineStr">
         <is>
           <t>조직표(인사표)에는 '목양관리'로 표기 — 같은 팀인지, 다른 팀인지 확인 필요</t>
         </is>
       </c>
-      <c r="H85" s="21" t="n"/>
-      <c r="I85" s="20" t="n"/>
-      <c r="J85" s="22" t="n"/>
-      <c r="K85" s="22" t="n"/>
-      <c r="L85" s="22" t="n"/>
-      <c r="M85" s="23" t="n"/>
-      <c r="N85" s="23" t="n"/>
-      <c r="O85" s="21" t="n"/>
-      <c r="P85" s="21" t="n"/>
-      <c r="Q85" s="21" t="n"/>
-      <c r="R85" s="21" t="n"/>
-      <c r="S85" s="21" t="n"/>
-      <c r="T85" s="21" t="n"/>
+      <c r="H85" s="23" t="n"/>
+      <c r="I85" s="22" t="n"/>
+      <c r="J85" s="24" t="n"/>
+      <c r="K85" s="24" t="n"/>
+      <c r="L85" s="24" t="n"/>
+      <c r="M85" s="25" t="n"/>
+      <c r="N85" s="24" t="n"/>
+      <c r="O85" s="25" t="n"/>
+      <c r="P85" s="24" t="n"/>
+      <c r="Q85" s="24" t="n"/>
+      <c r="R85" s="26" t="n"/>
+      <c r="S85" s="26" t="n"/>
+      <c r="T85" s="23" t="n"/>
+      <c r="U85" s="23" t="n"/>
+      <c r="V85" s="23" t="n"/>
+      <c r="W85" s="23" t="n"/>
+      <c r="X85" s="23" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="n">
+      <c r="A86" s="22" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="20" t="inlineStr">
+      <c r="B86" s="22" t="inlineStr">
         <is>
           <t>L-12(목양부)</t>
         </is>
       </c>
-      <c r="C86" s="20" t="n"/>
-      <c r="D86" s="21" t="inlineStr">
+      <c r="C86" s="22" t="n"/>
+      <c r="D86" s="23" t="inlineStr">
         <is>
           <t>소그룹 리더교육</t>
         </is>
       </c>
-      <c r="E86" s="20" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F86" s="21" t="n"/>
-      <c r="G86" s="21" t="inlineStr">
+      <c r="E86" s="22" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F86" s="23" t="n"/>
+      <c r="G86" s="23" t="inlineStr">
         <is>
           <t>조직표(인사표)에는 '서기'로 표기 — 같은 팀인지, 다른 팀인지 확인 필요</t>
         </is>
       </c>
-      <c r="H86" s="21" t="n"/>
-      <c r="I86" s="20" t="n"/>
-      <c r="J86" s="22" t="n"/>
-      <c r="K86" s="22" t="n"/>
-      <c r="L86" s="22" t="n"/>
-      <c r="M86" s="23" t="n"/>
-      <c r="N86" s="23" t="n"/>
-      <c r="O86" s="21" t="n"/>
-      <c r="P86" s="21" t="n"/>
-      <c r="Q86" s="21" t="n"/>
-      <c r="R86" s="21" t="n"/>
-      <c r="S86" s="21" t="n"/>
-      <c r="T86" s="21" t="n"/>
+      <c r="H86" s="23" t="n"/>
+      <c r="I86" s="22" t="n"/>
+      <c r="J86" s="24" t="n"/>
+      <c r="K86" s="24" t="n"/>
+      <c r="L86" s="24" t="n"/>
+      <c r="M86" s="25" t="n"/>
+      <c r="N86" s="24" t="n"/>
+      <c r="O86" s="25" t="n"/>
+      <c r="P86" s="24" t="n"/>
+      <c r="Q86" s="24" t="n"/>
+      <c r="R86" s="26" t="n"/>
+      <c r="S86" s="26" t="n"/>
+      <c r="T86" s="23" t="n"/>
+      <c r="U86" s="23" t="n"/>
+      <c r="V86" s="23" t="n"/>
+      <c r="W86" s="23" t="n"/>
+      <c r="X86" s="23" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="20" t="n">
+      <c r="A87" s="22" t="n">
         <v>85</v>
       </c>
-      <c r="B87" s="20" t="inlineStr">
+      <c r="B87" s="22" t="inlineStr">
         <is>
           <t>L-12(목양부)</t>
         </is>
       </c>
-      <c r="C87" s="20" t="n"/>
-      <c r="D87" s="21" t="inlineStr">
+      <c r="C87" s="22" t="n"/>
+      <c r="D87" s="23" t="inlineStr">
         <is>
           <t>회계</t>
         </is>
       </c>
-      <c r="E87" s="20" t="inlineStr">
+      <c r="E87" s="22" t="inlineStr">
         <is>
           <t>임명직</t>
         </is>
       </c>
-      <c r="F87" s="21" t="n"/>
-      <c r="G87" s="21" t="inlineStr">
+      <c r="F87" s="23" t="n"/>
+      <c r="G87" s="23" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있음 — 임명직인지 확인 필요</t>
         </is>
       </c>
-      <c r="H87" s="21" t="n"/>
-      <c r="I87" s="20" t="n"/>
-      <c r="J87" s="22" t="n"/>
-      <c r="K87" s="22" t="n"/>
-      <c r="L87" s="22" t="n"/>
-      <c r="M87" s="23" t="n"/>
-      <c r="N87" s="23" t="n"/>
-      <c r="O87" s="21" t="n"/>
-      <c r="P87" s="21" t="n"/>
-      <c r="Q87" s="21" t="n"/>
-      <c r="R87" s="21" t="n"/>
-      <c r="S87" s="21" t="n"/>
-      <c r="T87" s="21" t="n"/>
+      <c r="H87" s="23" t="n"/>
+      <c r="I87" s="22" t="n"/>
+      <c r="J87" s="24" t="n"/>
+      <c r="K87" s="24" t="n"/>
+      <c r="L87" s="24" t="n"/>
+      <c r="M87" s="25" t="n"/>
+      <c r="N87" s="24" t="n"/>
+      <c r="O87" s="25" t="n"/>
+      <c r="P87" s="24" t="n"/>
+      <c r="Q87" s="24" t="n"/>
+      <c r="R87" s="26" t="n"/>
+      <c r="S87" s="26" t="n"/>
+      <c r="T87" s="23" t="n"/>
+      <c r="U87" s="23" t="n"/>
+      <c r="V87" s="23" t="n"/>
+      <c r="W87" s="23" t="n"/>
+      <c r="X87" s="23" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n">
+      <c r="A88" s="17" t="n">
         <v>86</v>
       </c>
-      <c r="B88" s="16" t="inlineStr">
+      <c r="B88" s="17" t="inlineStr">
         <is>
           <t>L-12(목양부)</t>
         </is>
       </c>
-      <c r="C88" s="16" t="n"/>
-      <c r="D88" s="17" t="inlineStr">
+      <c r="C88" s="17" t="n"/>
+      <c r="D88" s="18" t="inlineStr">
         <is>
           <t>리더</t>
         </is>
       </c>
-      <c r="E88" s="16" t="inlineStr">
+      <c r="E88" s="17" t="inlineStr">
         <is>
           <t>임명직</t>
         </is>
       </c>
-      <c r="F88" s="17" t="n"/>
-      <c r="G88" s="17" t="n"/>
-      <c r="H88" s="17" t="n"/>
-      <c r="I88" s="16" t="n"/>
-      <c r="J88" s="18" t="n"/>
-      <c r="K88" s="18" t="n"/>
-      <c r="L88" s="18" t="n"/>
-      <c r="M88" s="19" t="n"/>
+      <c r="F88" s="18" t="n"/>
+      <c r="G88" s="18" t="n"/>
+      <c r="H88" s="18" t="n"/>
+      <c r="I88" s="17" t="n"/>
+      <c r="J88" s="19" t="n"/>
+      <c r="K88" s="19" t="n"/>
+      <c r="L88" s="19" t="n"/>
+      <c r="M88" s="20" t="n"/>
       <c r="N88" s="19" t="n"/>
-      <c r="O88" s="17" t="n"/>
-      <c r="P88" s="17" t="n"/>
-      <c r="Q88" s="17" t="n"/>
-      <c r="R88" s="17" t="n"/>
-      <c r="S88" s="17" t="n"/>
-      <c r="T88" s="17" t="n"/>
+      <c r="O88" s="20" t="n"/>
+      <c r="P88" s="19" t="n"/>
+      <c r="Q88" s="19" t="n"/>
+      <c r="R88" s="21" t="n"/>
+      <c r="S88" s="21" t="n"/>
+      <c r="T88" s="18" t="n"/>
+      <c r="U88" s="18" t="n"/>
+      <c r="V88" s="18" t="n"/>
+      <c r="W88" s="18" t="n"/>
+      <c r="X88" s="18" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
@@ -4213,13 +4590,17 @@
       <c r="K89" s="14" t="n"/>
       <c r="L89" s="14" t="n"/>
       <c r="M89" s="15" t="n"/>
-      <c r="N89" s="15" t="n"/>
-      <c r="O89" s="12" t="n"/>
-      <c r="P89" s="12" t="n"/>
-      <c r="Q89" s="12" t="n"/>
-      <c r="R89" s="12" t="n"/>
-      <c r="S89" s="12" t="n"/>
+      <c r="N89" s="14" t="n"/>
+      <c r="O89" s="15" t="n"/>
+      <c r="P89" s="14" t="n"/>
+      <c r="Q89" s="14" t="n"/>
+      <c r="R89" s="16" t="n"/>
+      <c r="S89" s="16" t="n"/>
       <c r="T89" s="12" t="n"/>
+      <c r="U89" s="12" t="n"/>
+      <c r="V89" s="12" t="n"/>
+      <c r="W89" s="12" t="n"/>
+      <c r="X89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="9" t="n">
@@ -4249,13 +4630,17 @@
       <c r="K90" s="14" t="n"/>
       <c r="L90" s="14" t="n"/>
       <c r="M90" s="15" t="n"/>
-      <c r="N90" s="15" t="n"/>
-      <c r="O90" s="12" t="n"/>
-      <c r="P90" s="12" t="n"/>
-      <c r="Q90" s="12" t="n"/>
-      <c r="R90" s="12" t="n"/>
-      <c r="S90" s="12" t="n"/>
+      <c r="N90" s="14" t="n"/>
+      <c r="O90" s="15" t="n"/>
+      <c r="P90" s="14" t="n"/>
+      <c r="Q90" s="14" t="n"/>
+      <c r="R90" s="16" t="n"/>
+      <c r="S90" s="16" t="n"/>
       <c r="T90" s="12" t="n"/>
+      <c r="U90" s="12" t="n"/>
+      <c r="V90" s="12" t="n"/>
+      <c r="W90" s="12" t="n"/>
+      <c r="X90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="9" t="n">
@@ -4285,49 +4670,57 @@
       <c r="K91" s="14" t="n"/>
       <c r="L91" s="14" t="n"/>
       <c r="M91" s="15" t="n"/>
-      <c r="N91" s="15" t="n"/>
-      <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="12" t="n"/>
-      <c r="R91" s="12" t="n"/>
-      <c r="S91" s="12" t="n"/>
+      <c r="N91" s="14" t="n"/>
+      <c r="O91" s="15" t="n"/>
+      <c r="P91" s="14" t="n"/>
+      <c r="Q91" s="14" t="n"/>
+      <c r="R91" s="16" t="n"/>
+      <c r="S91" s="16" t="n"/>
       <c r="T91" s="12" t="n"/>
+      <c r="U91" s="12" t="n"/>
+      <c r="V91" s="12" t="n"/>
+      <c r="W91" s="12" t="n"/>
+      <c r="X91" s="12" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n">
+      <c r="A92" s="17" t="n">
         <v>90</v>
       </c>
-      <c r="B92" s="16" t="inlineStr">
+      <c r="B92" s="17" t="inlineStr">
         <is>
           <t>총무부</t>
         </is>
       </c>
-      <c r="C92" s="16" t="n"/>
-      <c r="D92" s="17" t="inlineStr">
+      <c r="C92" s="17" t="n"/>
+      <c r="D92" s="18" t="inlineStr">
         <is>
           <t>상담실</t>
         </is>
       </c>
-      <c r="E92" s="16" t="inlineStr">
+      <c r="E92" s="17" t="inlineStr">
         <is>
           <t>임명직</t>
         </is>
       </c>
-      <c r="F92" s="17" t="n"/>
-      <c r="G92" s="17" t="n"/>
-      <c r="H92" s="17" t="n"/>
-      <c r="I92" s="16" t="n"/>
-      <c r="J92" s="18" t="n"/>
-      <c r="K92" s="18" t="n"/>
-      <c r="L92" s="18" t="n"/>
-      <c r="M92" s="19" t="n"/>
+      <c r="F92" s="18" t="n"/>
+      <c r="G92" s="18" t="n"/>
+      <c r="H92" s="18" t="n"/>
+      <c r="I92" s="17" t="n"/>
+      <c r="J92" s="19" t="n"/>
+      <c r="K92" s="19" t="n"/>
+      <c r="L92" s="19" t="n"/>
+      <c r="M92" s="20" t="n"/>
       <c r="N92" s="19" t="n"/>
-      <c r="O92" s="17" t="n"/>
-      <c r="P92" s="17" t="n"/>
-      <c r="Q92" s="17" t="n"/>
-      <c r="R92" s="17" t="n"/>
-      <c r="S92" s="17" t="n"/>
-      <c r="T92" s="17" t="n"/>
+      <c r="O92" s="20" t="n"/>
+      <c r="P92" s="19" t="n"/>
+      <c r="Q92" s="19" t="n"/>
+      <c r="R92" s="21" t="n"/>
+      <c r="S92" s="21" t="n"/>
+      <c r="T92" s="18" t="n"/>
+      <c r="U92" s="18" t="n"/>
+      <c r="V92" s="18" t="n"/>
+      <c r="W92" s="18" t="n"/>
+      <c r="X92" s="18" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="9" t="n">
@@ -4357,13 +4750,17 @@
       <c r="K93" s="14" t="n"/>
       <c r="L93" s="14" t="n"/>
       <c r="M93" s="15" t="n"/>
-      <c r="N93" s="15" t="n"/>
-      <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
-      <c r="Q93" s="12" t="n"/>
-      <c r="R93" s="12" t="n"/>
-      <c r="S93" s="12" t="n"/>
+      <c r="N93" s="14" t="n"/>
+      <c r="O93" s="15" t="n"/>
+      <c r="P93" s="14" t="n"/>
+      <c r="Q93" s="14" t="n"/>
+      <c r="R93" s="16" t="n"/>
+      <c r="S93" s="16" t="n"/>
       <c r="T93" s="12" t="n"/>
+      <c r="U93" s="12" t="n"/>
+      <c r="V93" s="12" t="n"/>
+      <c r="W93" s="12" t="n"/>
+      <c r="X93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="9" t="n">
@@ -4393,13 +4790,17 @@
       <c r="K94" s="14" t="n"/>
       <c r="L94" s="14" t="n"/>
       <c r="M94" s="15" t="n"/>
-      <c r="N94" s="15" t="n"/>
-      <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
-      <c r="Q94" s="12" t="n"/>
-      <c r="R94" s="12" t="n"/>
-      <c r="S94" s="12" t="n"/>
+      <c r="N94" s="14" t="n"/>
+      <c r="O94" s="15" t="n"/>
+      <c r="P94" s="14" t="n"/>
+      <c r="Q94" s="14" t="n"/>
+      <c r="R94" s="16" t="n"/>
+      <c r="S94" s="16" t="n"/>
       <c r="T94" s="12" t="n"/>
+      <c r="U94" s="12" t="n"/>
+      <c r="V94" s="12" t="n"/>
+      <c r="W94" s="12" t="n"/>
+      <c r="X94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="9" t="n">
@@ -4429,13 +4830,17 @@
       <c r="K95" s="14" t="n"/>
       <c r="L95" s="14" t="n"/>
       <c r="M95" s="15" t="n"/>
-      <c r="N95" s="15" t="n"/>
-      <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
-      <c r="Q95" s="12" t="n"/>
-      <c r="R95" s="12" t="n"/>
-      <c r="S95" s="12" t="n"/>
+      <c r="N95" s="14" t="n"/>
+      <c r="O95" s="15" t="n"/>
+      <c r="P95" s="14" t="n"/>
+      <c r="Q95" s="14" t="n"/>
+      <c r="R95" s="16" t="n"/>
+      <c r="S95" s="16" t="n"/>
       <c r="T95" s="12" t="n"/>
+      <c r="U95" s="12" t="n"/>
+      <c r="V95" s="12" t="n"/>
+      <c r="W95" s="12" t="n"/>
+      <c r="X95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="9" t="n">
@@ -4465,24 +4870,28 @@
       <c r="K96" s="14" t="n"/>
       <c r="L96" s="14" t="n"/>
       <c r="M96" s="15" t="n"/>
-      <c r="N96" s="15" t="n"/>
-      <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="12" t="n"/>
-      <c r="R96" s="12" t="n"/>
-      <c r="S96" s="12" t="n"/>
+      <c r="N96" s="14" t="n"/>
+      <c r="O96" s="15" t="n"/>
+      <c r="P96" s="14" t="n"/>
+      <c r="Q96" s="14" t="n"/>
+      <c r="R96" s="16" t="n"/>
+      <c r="S96" s="16" t="n"/>
       <c r="T96" s="12" t="n"/>
+      <c r="U96" s="12" t="n"/>
+      <c r="V96" s="12" t="n"/>
+      <c r="W96" s="12" t="n"/>
+      <c r="X96" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T96"/>
+  <autoFilter ref="A2:X96"/>
   <mergeCells count="5">
-    <mergeCell ref="P1:R1"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="J1:S1"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="9">
     <dataValidation sqref="I3:I96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="유지 / 이름 수정 / 신설 / 폐지 중 선택" type="list">
       <formula1>"유지,이름 수정,신설,폐지"</formula1>
     </dataValidation>
@@ -4495,8 +4904,20 @@
     <dataValidation sqref="L3:L96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="이 요일에 사역하면 O (아니면 비워 두세요)" type="list">
       <formula1>"O"</formula1>
     </dataValidation>
-    <dataValidation sqref="O3:O96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다)" type="list">
-      <formula1>"매주,격주,매달,그때그때"</formula1>
+    <dataValidation sqref="M3:M96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="이 요일에 사역하면 O (아니면 비워 두세요)" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N3:N96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다). 여럿이면 여럿 다 O" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다). 여럿이면 여럿 다 O" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P3:P96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다). 여럿이면 여럿 다 O" type="list">
+      <formula1>"O"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q3:Q96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="O 만 넣어 주세요" prompt="한 분이 실제로 서는 주기입니다 (팀이 모이는 주기가 아닙니다). 여럿이면 여럿 다 O" type="list">
+      <formula1>"O"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4529,48 +4950,48 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>M-12부</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>신청서에 개별 사역팀 없음 — 행정운영/리더 전원 임명직</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>재정부</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>신청 대상 없음 — 회계·계수·재무 전원 임명직</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>감사위원회</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>신청 대상 없음 — 감사위원 임명직</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>당회 · 제직회</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>담임목사 직속 기구 — 사역신청서 대상 아님</t>
         </is>
